--- a/Design/Configs/Effect.xlsx
+++ b/Design/Configs/Effect.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B909FDF-7919-4077-9799-E57B3C935C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBC4A31-D264-4FE0-B651-7F1DD57D13A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="480" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="-30" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -33,35 +33,12 @@
     <t>EffectTypeId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>[1,2,4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[1,2,5]</t>
-  </si>
-  <si>
-    <t>[1,2,6]</t>
-  </si>
-  <si>
-    <t>[1,2,7]</t>
-  </si>
-  <si>
-    <t>[1,2,8]</t>
-  </si>
-  <si>
-    <t>[1,2,9]</t>
-  </si>
-  <si>
-    <t>Params</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +48,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -97,8 +83,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -379,12 +372,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.25" customWidth="1"/>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="1" max="1" width="25.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="25.25" customWidth="1"/>
     <col min="5" max="5" width="14.375" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
@@ -393,102 +386,81 @@
     <col min="9" max="9" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>1001</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>1001</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>1001</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>1001</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1001</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1001</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
